--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,6 +2036,4507 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128574141</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 42892, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6397216</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128573633</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 42892, Storön, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577299</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6397392</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128573425</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 42892, Storön, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577301</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6397387</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128573533</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 42892, Storön, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577299</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6397392</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128574449</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 42892, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577571</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6396971</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128574258</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 42892, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577439</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6397139</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128587379</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577534</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6397198</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128588320</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577330</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6397251</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128587161</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577587</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6397168</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128587653</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577528</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6397197</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128589365</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577563</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6397121</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128589051</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>577526</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6397201</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128589413</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>577551</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6397114</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128589098</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577559</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6397176</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128589117</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>577567</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6397167</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128588351</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>577334</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6397251</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128589202</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>577556</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6397147</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128589873</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92084</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>577335</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6397526</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128588407</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>577325</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6397295</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128588522</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>577319</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6397313</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128587353</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>577540</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6397185</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128589707</v>
+      </c>
+      <c r="B35" t="n">
+        <v>105609</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6397344</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128589543</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>577317</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6397198</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128587466</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>577524</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6397211</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128589077</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>577525</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6397189</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128588456</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>577392</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6397117</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128588564</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>577316</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6397317</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128589031</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>577525</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6397206</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128589604</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>577299</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6397221</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128589315</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>577563</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6397129</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128589521</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>577320</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6397185</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128588364</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>577326</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6397406</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128588509</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92084</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>577342</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6397146</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128589006</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>577523</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6397214</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128588696</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>577297</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6397374</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128588384</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>577333</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6397265</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128589459</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>577497</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6397021</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128588387</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>577332</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6397322</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128588492</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>577314</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6397299</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128587948</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>577405</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6397127</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128587548</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>577533</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6397187</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128589521</v>
+        <v>128588364</v>
       </c>
       <c r="B44" t="n">
         <v>98571</v>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5374,14 +5374,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577320</v>
+        <v>577326</v>
       </c>
       <c r="R44" t="n">
-        <v>6397185</v>
+        <v>6397406</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,19 +5429,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128588364</v>
+        <v>128589521</v>
       </c>
       <c r="B45" t="n">
         <v>98571</v>
@@ -5471,12 +5471,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -5484,14 +5484,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577326</v>
+        <v>577320</v>
       </c>
       <c r="R45" t="n">
-        <v>6397406</v>
+        <v>6397185</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5539,12 +5539,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6203,53 +6203,53 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128588492</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577314</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397299</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,7 +6301,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6320,46 +6319,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6367,10 +6366,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6411,6 +6410,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
         <v>98571</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3675,14 +3675,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
         <v>98571</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -6210,46 +6210,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B52" t="n">
-        <v>57682</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R52" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,6 +6301,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6319,7 +6320,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B53" t="n">
         <v>98571</v>
@@ -6349,12 +6350,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6363,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,69 +6418,69 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>57682</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,19 +6521,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>128573425</v>
       </c>
       <c r="B16" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>128573533</v>
       </c>
       <c r="B17" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4224,49 +4224,49 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>105621</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R34" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,54 +4329,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>105609</v>
+        <v>98579</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R35" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,12 +4439,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92084</v>
+        <v>92090</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R48" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R49" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R50" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R51" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,58 +6198,58 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128588492</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>57686</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577314</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397299</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,7 +6301,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6323,7 +6322,7 @@
         <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6430,46 +6429,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6477,10 +6476,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,6 +6520,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R22" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R23" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B28" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R28" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R29" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3902,45 +3902,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128589873</v>
+        <v>128588407</v>
       </c>
       <c r="B31" t="n">
-        <v>92090</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3948,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577335</v>
+        <v>577325</v>
       </c>
       <c r="R31" t="n">
-        <v>6397526</v>
+        <v>6397295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4011,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128588407</v>
+        <v>128588522</v>
       </c>
       <c r="B32" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4042,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4058,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577325</v>
+        <v>577319</v>
       </c>
       <c r="R32" t="n">
-        <v>6397295</v>
+        <v>6397313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4121,46 +4122,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128588522</v>
+        <v>128589873</v>
       </c>
       <c r="B33" t="n">
-        <v>98579</v>
+        <v>92096</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577319</v>
+        <v>577335</v>
       </c>
       <c r="R33" t="n">
-        <v>6397313</v>
+        <v>6397526</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4224,49 +4224,49 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B34" t="n">
-        <v>105621</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R34" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,54 +4329,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B35" t="n">
-        <v>98579</v>
+        <v>105630</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R35" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,12 +4439,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588564</v>
+        <v>128588456</v>
       </c>
       <c r="B39" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577316</v>
+        <v>577392</v>
       </c>
       <c r="R39" t="n">
-        <v>6397317</v>
+        <v>6397117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128589031</v>
+        <v>128588564</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577525</v>
+        <v>577316</v>
       </c>
       <c r="R40" t="n">
-        <v>6397206</v>
+        <v>6397317</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588456</v>
+        <v>128589031</v>
       </c>
       <c r="B41" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577392</v>
+        <v>577525</v>
       </c>
       <c r="R41" t="n">
-        <v>6397117</v>
+        <v>6397206</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B48" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R48" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B49" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R49" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5983,17 +5983,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B50" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R50" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B51" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R51" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,12 +6198,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,22 +6417,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B54" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6472,14 +6472,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R54" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6527,12 +6527,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3902,46 +3902,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128588407</v>
+        <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>92098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3949,10 +3948,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577325</v>
+        <v>577335</v>
       </c>
       <c r="R31" t="n">
-        <v>6397295</v>
+        <v>6397526</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4012,10 +4011,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128588522</v>
+        <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4041,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577319</v>
+        <v>577325</v>
       </c>
       <c r="R32" t="n">
-        <v>6397313</v>
+        <v>6397295</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4122,45 +4121,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128589873</v>
+        <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>92096</v>
+        <v>98588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577335</v>
+        <v>577319</v>
       </c>
       <c r="R33" t="n">
-        <v>6397526</v>
+        <v>6397313</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
         <v>128587353</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4341,37 +4341,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589707</v>
+        <v>128589543</v>
       </c>
       <c r="B35" t="n">
-        <v>105630</v>
+        <v>98588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577302</v>
+        <v>577317</v>
       </c>
       <c r="R35" t="n">
-        <v>6397344</v>
+        <v>6397198</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4451,37 +4451,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128589543</v>
+        <v>128589707</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>105642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577317</v>
+        <v>577302</v>
       </c>
       <c r="R36" t="n">
-        <v>6397198</v>
+        <v>6397344</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R48" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R49" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R50" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R51" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,12 +6198,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,22 +6417,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6472,14 +6472,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6527,15 +6527,761 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128746752</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92752</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>577493</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6396740</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand , Magnus Kasselstrand, Mats Oldenborg, Eddy Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128746398</v>
+      </c>
+      <c r="B56" t="n">
+        <v>105642</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>A 42892, Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>577523</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6396657</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128745964</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>577621</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6396591</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128747154</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>577532</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6396903</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128747224</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>577512</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6396938</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128746440</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92095</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>A 42892, Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>577567</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6397014</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128745659</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>577635</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6396627</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,52 +3895,53 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128589873</v>
+        <v>128588407</v>
       </c>
       <c r="B31" t="n">
-        <v>92098</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3948,10 +3949,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577335</v>
+        <v>577325</v>
       </c>
       <c r="R31" t="n">
-        <v>6397526</v>
+        <v>6397295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4011,10 +4012,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128588407</v>
+        <v>128588522</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4041,7 +4042,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4058,10 +4059,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577325</v>
+        <v>577319</v>
       </c>
       <c r="R32" t="n">
-        <v>6397295</v>
+        <v>6397313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4121,46 +4122,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128588522</v>
+        <v>128589873</v>
       </c>
       <c r="B33" t="n">
-        <v>98588</v>
+        <v>92098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577319</v>
+        <v>577335</v>
       </c>
       <c r="R33" t="n">
-        <v>6397313</v>
+        <v>6397526</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4231,42 +4231,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>105651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R34" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,22 +4329,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589543</v>
+        <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577317</v>
+        <v>577540</v>
       </c>
       <c r="R35" t="n">
-        <v>6397198</v>
+        <v>6397185</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,49 +4439,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128589707</v>
+        <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>105642</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577302</v>
+        <v>577317</v>
       </c>
       <c r="R36" t="n">
-        <v>6397344</v>
+        <v>6397198</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,57 +6210,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587948</v>
+        <v>128587548</v>
       </c>
       <c r="B52" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577405</v>
+        <v>577533</v>
       </c>
       <c r="R52" t="n">
-        <v>6397127</v>
+        <v>6397187</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,28 +6301,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,12 +6350,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6363,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,58 +6418,58 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128588492</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98588</v>
+        <v>57686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6476,10 +6477,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577314</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397299</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,7 +6521,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6539,10 +6539,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128746752</v>
+        <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>92752</v>
+        <v>105651</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6550,44 +6550,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4363</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Storö, Sm</t>
+          <t>A 42892, Storö, Sm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>577493</v>
+        <v>577523</v>
       </c>
       <c r="R55" t="n">
-        <v>6396740</v>
+        <v>6396657</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6632,22 +6633,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand , Magnus Kasselstrand, Mats Oldenborg, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128746398</v>
+        <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>105642</v>
+        <v>92163</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6655,45 +6656,44 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>3298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>A 42892, Storö, Sm</t>
+          <t>Storö, Sm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>577523</v>
+        <v>577621</v>
       </c>
       <c r="R56" t="n">
-        <v>6396657</v>
+        <v>6396591</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6738,52 +6738,48 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128745964</v>
+        <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>92163</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6792,10 +6788,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>577621</v>
+        <v>577532</v>
       </c>
       <c r="R57" t="n">
-        <v>6396591</v>
+        <v>6396903</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6830,6 +6826,11 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>rikligt på flera träd</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6848,58 +6849,66 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128747154</v>
+        <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>92095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1339</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Storö, Sm</t>
+          <t>A 42892, Storö, Sm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577532</v>
+        <v>577567</v>
       </c>
       <c r="R58" t="n">
-        <v>6396903</v>
+        <v>6397014</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6929,11 +6938,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>rikligt på flera träd</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6949,48 +6953,56 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128747224</v>
+        <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>92163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
@@ -6999,13 +7011,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577512</v>
+        <v>577635</v>
       </c>
       <c r="R59" t="n">
-        <v>6396938</v>
+        <v>6396627</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7035,11 +7047,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7060,66 +7067,66 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128746440</v>
+        <v>128750696</v>
       </c>
       <c r="B60" t="n">
-        <v>92095</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1339</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>A 42892, Storö, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577567</v>
+        <v>577547</v>
       </c>
       <c r="R60" t="n">
-        <v>6397014</v>
+        <v>6397047</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7164,22 +7171,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128745659</v>
+        <v>128746752</v>
       </c>
       <c r="B61" t="n">
-        <v>92163</v>
+        <v>92752</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7187,28 +7194,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3298</v>
+        <v>4363</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -7222,10 +7225,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577635</v>
+        <v>577493</v>
       </c>
       <c r="R61" t="n">
-        <v>6396627</v>
+        <v>6396740</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7278,10 +7281,3861 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Stefan Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand , Magnus Kasselstrand, Mats Oldenborg, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128750200</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>577536</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6396632</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128750664</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91426</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>577487</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6396834</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128750128</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>577579</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6397094</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128750627</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91426</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>577616</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6397020</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128750295</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>577565</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6396643</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128749468</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>577505</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6397030</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128749315</v>
+      </c>
+      <c r="B68" t="n">
+        <v>105651</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>577496</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6396668</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128749427</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>577573</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6396656</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128749919</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>577553</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6396625</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128751010</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57849</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>577576</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6397011</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128751121</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>577552</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6397031</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128749762</v>
+      </c>
+      <c r="B73" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>577520</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6397206</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128749963</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>577550</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6396640</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128750252</v>
+      </c>
+      <c r="B75" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>577586</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6397020</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128750116</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>577597</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6396639</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128750104</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>577547</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6396625</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128749932</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>577570</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6397099</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128749391</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>577496</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6396679</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128750565</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92098</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>577543</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6397141</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128750187</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>577604</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6396634</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128750392</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>577572</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6397209</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128749790</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>577562</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6397209</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128747224</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>577512</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6396938</v>
+      </c>
+      <c r="S84" t="n">
+        <v>25</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128749840</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>577555</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6397202</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128750312</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>577536</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6397202</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128749795</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>577528</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6397203</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128750043</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>577551</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6396649</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128749486</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>577547</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6397046</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128749756</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>577557</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6397045</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128750513</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91876</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>577549</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6396635</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128750272</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>577568</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6397011</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128749441</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79283</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1639</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blomskägglav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Usnea florida</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Storö, Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>577481</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6396802</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128749939</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>577580</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6397024</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128750368</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>577555</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6396639</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128750413</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>577572</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6396641</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6210,7 +6210,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B52" t="n">
         <v>98591</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -6253,14 +6253,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R52" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6308,58 +6308,58 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587948</v>
       </c>
       <c r="B53" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577405</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397127</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6411,7 +6411,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6430,57 +6429,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128587548</v>
       </c>
       <c r="B54" t="n">
-        <v>57686</v>
+        <v>98591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577533</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397187</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,18 +6520,19 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -9280,45 +9280,46 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128750565</v>
+        <v>128750187</v>
       </c>
       <c r="B80" t="n">
-        <v>92098</v>
+        <v>98591</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9326,10 +9327,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577543</v>
+        <v>577604</v>
       </c>
       <c r="R80" t="n">
-        <v>6397141</v>
+        <v>6396634</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9389,7 +9390,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128750187</v>
+        <v>128750392</v>
       </c>
       <c r="B81" t="n">
         <v>98591</v>
@@ -9419,7 +9420,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9436,10 +9437,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577604</v>
+        <v>577572</v>
       </c>
       <c r="R81" t="n">
-        <v>6396634</v>
+        <v>6397209</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9499,7 +9500,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128750392</v>
+        <v>128749790</v>
       </c>
       <c r="B82" t="n">
         <v>98591</v>
@@ -9529,7 +9530,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -9546,7 +9547,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577572</v>
+        <v>577562</v>
       </c>
       <c r="R82" t="n">
         <v>6397209</v>
@@ -9609,60 +9610,51 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128749790</v>
+        <v>128747224</v>
       </c>
       <c r="B83" t="n">
-        <v>98591</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Sm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577562</v>
+        <v>577512</v>
       </c>
       <c r="R83" t="n">
-        <v>6397209</v>
+        <v>6396938</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9692,6 +9684,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9707,63 +9704,71 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128747224</v>
+        <v>128750565</v>
       </c>
       <c r="B84" t="n">
-        <v>79089</v>
+        <v>92098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6031</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Storö, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>577512</v>
+        <v>577543</v>
       </c>
       <c r="R84" t="n">
-        <v>6396938</v>
+        <v>6397141</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9793,11 +9798,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9813,12 +9813,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Eddy Kasselstrand, Gunilla Nilsson, Magnus Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,53 +3895,52 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128588407</v>
+        <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>98591</v>
+        <v>92099</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3949,10 +3948,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577325</v>
+        <v>577335</v>
       </c>
       <c r="R31" t="n">
-        <v>6397295</v>
+        <v>6397526</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4012,10 +4011,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128588522</v>
+        <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4042,7 +4041,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4059,10 +4058,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577319</v>
+        <v>577325</v>
       </c>
       <c r="R32" t="n">
-        <v>6397313</v>
+        <v>6397295</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4122,45 +4121,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128589873</v>
+        <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>92098</v>
+        <v>98592</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>577335</v>
+        <v>577319</v>
       </c>
       <c r="R33" t="n">
-        <v>6397526</v>
+        <v>6397313</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4234,7 +4234,7 @@
         <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
         <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5004,7 +5004,7 @@
         <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,10 +6210,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B52" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -6253,14 +6253,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R52" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6308,58 +6308,58 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>57686</v>
+        <v>98592</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6411,6 +6411,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6429,57 +6430,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98591</v>
+        <v>57686</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,19 +6521,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92095</v>
+        <v>92096</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
         <v>128573425</v>
       </c>
       <c r="B16" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>128573533</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4344,7 +4344,7 @@
         <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6210,57 +6210,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98592</v>
+        <v>57713</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,29 +6301,28 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6350,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6363,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6418,58 +6417,58 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>57686</v>
+        <v>98619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6477,10 +6476,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,6 +6520,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Eddy Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92096</v>
+        <v>92123</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Eddy Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4231,42 +4231,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B34" t="n">
-        <v>105682</v>
+        <v>98625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R34" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,22 +4329,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128587353</v>
+        <v>128589543</v>
       </c>
       <c r="B35" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577540</v>
+        <v>577317</v>
       </c>
       <c r="R35" t="n">
-        <v>6397185</v>
+        <v>6397198</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,49 +4439,49 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128589543</v>
+        <v>128589707</v>
       </c>
       <c r="B36" t="n">
-        <v>98619</v>
+        <v>105688</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577317</v>
+        <v>577302</v>
       </c>
       <c r="R36" t="n">
-        <v>6397198</v>
+        <v>6397344</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4784,7 +4784,7 @@
         <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5004,7 +5004,7 @@
         <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92123</v>
+        <v>92128</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128587353</v>
       </c>
       <c r="B34" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>128589543</v>
       </c>
       <c r="B35" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128589707</v>
       </c>
       <c r="B36" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
         <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92128</v>
+        <v>92133</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11137,6 +11137,116 @@
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128895504</v>
+      </c>
+      <c r="B97" t="n">
+        <v>96074</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>210</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Storö-Ankarsrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>577543</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6396644</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Stefan Kasselstrand, Sofia  Kasselstrand , Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B22" t="n">
         <v>98632</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R22" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B23" t="n">
         <v>98632</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R23" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B28" t="n">
         <v>98632</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R28" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B29" t="n">
         <v>98632</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R29" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4341,37 +4341,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589543</v>
+        <v>128589707</v>
       </c>
       <c r="B35" t="n">
-        <v>98632</v>
+        <v>105695</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577317</v>
+        <v>577302</v>
       </c>
       <c r="R35" t="n">
-        <v>6397198</v>
+        <v>6397344</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4451,37 +4451,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128589707</v>
+        <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>105695</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>577302</v>
+        <v>577317</v>
       </c>
       <c r="R36" t="n">
-        <v>6397344</v>
+        <v>6397198</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588564</v>
+        <v>128588456</v>
       </c>
       <c r="B39" t="n">
         <v>98632</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577316</v>
+        <v>577392</v>
       </c>
       <c r="R39" t="n">
-        <v>6397317</v>
+        <v>6397117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,19 +4879,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128589031</v>
+        <v>128588564</v>
       </c>
       <c r="B40" t="n">
         <v>98632</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577525</v>
+        <v>577316</v>
       </c>
       <c r="R40" t="n">
-        <v>6397206</v>
+        <v>6397317</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588456</v>
+        <v>128589031</v>
       </c>
       <c r="B41" t="n">
         <v>98632</v>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577392</v>
+        <v>577525</v>
       </c>
       <c r="R41" t="n">
-        <v>6397117</v>
+        <v>6397206</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B48" t="n">
         <v>98632</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R48" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B49" t="n">
         <v>98632</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R49" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B50" t="n">
         <v>98632</v>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R50" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,19 +6088,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B51" t="n">
         <v>98632</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R51" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,12 +6198,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
         <v>98632</v>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,19 +6417,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B54" t="n">
         <v>98632</v>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6472,14 +6472,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R54" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6527,12 +6527,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
         <v>128573425</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>128573533</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4231,42 +4231,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>98632</v>
+        <v>105699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R34" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,54 +4329,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>105695</v>
+        <v>98636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R35" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,12 +4439,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B39" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B40" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B41" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R48" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R49" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R50" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R51" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,69 +6198,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587948</v>
+        <v>128587548</v>
       </c>
       <c r="B52" t="n">
-        <v>57713</v>
+        <v>98636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577405</v>
+        <v>577533</v>
       </c>
       <c r="R52" t="n">
-        <v>6397127</v>
+        <v>6397187</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,18 +6301,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6322,7 +6323,7 @@
         <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6429,57 +6430,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98632</v>
+        <v>57717</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,19 +6521,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Eddy Kasselstrand, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92133</v>
+        <v>92137</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589413</v>
+        <v>128589098</v>
       </c>
       <c r="B26" t="n">
         <v>98636</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577551</v>
+        <v>577559</v>
       </c>
       <c r="R26" t="n">
-        <v>6397114</v>
+        <v>6397176</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589098</v>
+        <v>128589413</v>
       </c>
       <c r="B27" t="n">
         <v>98636</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577559</v>
+        <v>577551</v>
       </c>
       <c r="R27" t="n">
-        <v>6397176</v>
+        <v>6397114</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B28" t="n">
         <v>98636</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R28" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B29" t="n">
         <v>98636</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R29" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B39" t="n">
         <v>98636</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R39" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4884,14 +4884,14 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B40" t="n">
         <v>98636</v>
@@ -4921,12 +4921,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4934,14 +4934,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R40" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4989,19 +4989,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B41" t="n">
         <v>98636</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R41" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6210,57 +6210,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98636</v>
+        <v>57717</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,26 +6301,25 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B53" t="n">
         <v>98636</v>
@@ -6350,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6363,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6418,58 +6417,58 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>57717</v>
+        <v>98636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6477,10 +6476,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,6 +6520,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Eddy Kasselstrand, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Eddy Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588320</v>
+        <v>128587653</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2845,14 +2845,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577330</v>
+        <v>577528</v>
       </c>
       <c r="R21" t="n">
-        <v>6397251</v>
+        <v>6397197</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,19 +2900,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R22" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587161</v>
+        <v>128588320</v>
       </c>
       <c r="B23" t="n">
         <v>98636</v>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577587</v>
+        <v>577330</v>
       </c>
       <c r="R23" t="n">
-        <v>6397168</v>
+        <v>6397251</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128589098</v>
+        <v>128589413</v>
       </c>
       <c r="B26" t="n">
         <v>98636</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577559</v>
+        <v>577551</v>
       </c>
       <c r="R26" t="n">
-        <v>6397176</v>
+        <v>6397114</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128589413</v>
+        <v>128589098</v>
       </c>
       <c r="B27" t="n">
         <v>98636</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577551</v>
+        <v>577559</v>
       </c>
       <c r="R27" t="n">
-        <v>6397114</v>
+        <v>6397176</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
         <v>98636</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
         <v>98636</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B39" t="n">
         <v>98636</v>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R39" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,19 +4879,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B40" t="n">
         <v>98636</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4934,14 +4934,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R40" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4989,19 +4989,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B41" t="n">
         <v>98636</v>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R41" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128589604</v>
+        <v>128588364</v>
       </c>
       <c r="B42" t="n">
         <v>98636</v>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5154,14 +5154,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577299</v>
+        <v>577326</v>
       </c>
       <c r="R42" t="n">
-        <v>6397221</v>
+        <v>6397406</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5209,19 +5209,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128589315</v>
+        <v>128589604</v>
       </c>
       <c r="B43" t="n">
         <v>98636</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577563</v>
+        <v>577299</v>
       </c>
       <c r="R43" t="n">
-        <v>6397129</v>
+        <v>6397221</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128588364</v>
+        <v>128589315</v>
       </c>
       <c r="B44" t="n">
         <v>98636</v>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5374,14 +5374,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577326</v>
+        <v>577563</v>
       </c>
       <c r="R44" t="n">
-        <v>6397406</v>
+        <v>6397129</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,12 +5429,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2261,7 +2261,7 @@
         <v>128573425</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>128573533</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Eddy Kasselstrand, Magnus Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128587653</v>
+        <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2845,14 +2845,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577528</v>
+        <v>577330</v>
       </c>
       <c r="R21" t="n">
-        <v>6397197</v>
+        <v>6397251</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,22 +2900,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128588320</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577330</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397251</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>128588351</v>
       </c>
       <c r="B28" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>128589117</v>
       </c>
       <c r="B29" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128589031</v>
       </c>
       <c r="B39" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577525</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397206</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128588456</v>
       </c>
       <c r="B40" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4934,14 +4934,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577392</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397117</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4989,22 +4989,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588564</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577316</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397317</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128588364</v>
+        <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5154,14 +5154,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577326</v>
+        <v>577299</v>
       </c>
       <c r="R42" t="n">
-        <v>6397406</v>
+        <v>6397221</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5209,22 +5209,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128589604</v>
+        <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577299</v>
+        <v>577563</v>
       </c>
       <c r="R43" t="n">
-        <v>6397221</v>
+        <v>6397129</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5324,17 +5324,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128589315</v>
+        <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5374,14 +5374,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577563</v>
+        <v>577326</v>
       </c>
       <c r="R44" t="n">
-        <v>6397129</v>
+        <v>6397406</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,12 +5429,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>128588384</v>
       </c>
       <c r="B48" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>128588696</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>128588387</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>128589459</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128587548</v>
       </c>
       <c r="B53" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92137</v>
+        <v>92142</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>128588320</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R22" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B23" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R23" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B28" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R28" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B29" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R29" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4231,42 +4231,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B34" t="n">
-        <v>105709</v>
+        <v>98651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R34" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,54 +4329,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B35" t="n">
-        <v>98646</v>
+        <v>105714</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R35" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,12 +4439,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,10 +4781,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588564</v>
+        <v>128588456</v>
       </c>
       <c r="B39" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577316</v>
+        <v>577392</v>
       </c>
       <c r="R39" t="n">
-        <v>6397317</v>
+        <v>6397117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128589031</v>
+        <v>128588564</v>
       </c>
       <c r="B40" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577525</v>
+        <v>577316</v>
       </c>
       <c r="R40" t="n">
-        <v>6397206</v>
+        <v>6397317</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,10 +5001,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588456</v>
+        <v>128589031</v>
       </c>
       <c r="B41" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577392</v>
+        <v>577525</v>
       </c>
       <c r="R41" t="n">
-        <v>6397117</v>
+        <v>6397206</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
         <v>128589604</v>
       </c>
       <c r="B42" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>128589315</v>
       </c>
       <c r="B43" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>128588364</v>
       </c>
       <c r="B44" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B48" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R48" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B49" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R49" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B50" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R50" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B51" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R51" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,12 +6198,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6312,17 +6312,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128587548</v>
+        <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6362,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577533</v>
+        <v>577314</v>
       </c>
       <c r="R53" t="n">
-        <v>6397187</v>
+        <v>6397299</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,22 +6417,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B54" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -6472,14 +6472,14 @@
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R54" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6527,12 +6527,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2912,7 +2912,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
         <v>98651</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
         <v>98651</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3565,14 +3565,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
         <v>98651</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
         <v>98651</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4231,42 +4231,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128587353</v>
+        <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>98651</v>
+        <v>105714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577540</v>
+        <v>577302</v>
       </c>
       <c r="R34" t="n">
-        <v>6397185</v>
+        <v>6397344</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4329,54 +4329,54 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128589707</v>
+        <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>105714</v>
+        <v>98651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4384,14 +4384,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577302</v>
+        <v>577540</v>
       </c>
       <c r="R35" t="n">
-        <v>6397344</v>
+        <v>6397185</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,12 +4439,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4774,14 +4774,14 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B39" t="n">
         <v>98651</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,19 +4879,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B40" t="n">
         <v>98651</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B41" t="n">
         <v>98651</v>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,12 +5099,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B48" t="n">
         <v>98651</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R48" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B49" t="n">
         <v>98651</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R49" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B50" t="n">
         <v>98651</v>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R50" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,19 +6088,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B51" t="n">
         <v>98651</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R51" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,69 +6198,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587948</v>
+        <v>128587548</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>98651</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577405</v>
+        <v>577533</v>
       </c>
       <c r="R52" t="n">
-        <v>6397127</v>
+        <v>6397187</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,18 +6301,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6429,57 +6430,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,19 +6521,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105714</v>
+        <v>105719</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92150</v>
+        <v>92155</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96093</v>
+        <v>96098</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2041,7 +2041,7 @@
         <v>128574141</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>128573633</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>128574449</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>128574258</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
         <v>128587379</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,10 +2802,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128588320</v>
+        <v>128587653</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2845,14 +2845,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577330</v>
+        <v>577528</v>
       </c>
       <c r="R21" t="n">
-        <v>6397251</v>
+        <v>6397197</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,22 +2900,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587653</v>
+        <v>128587161</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577528</v>
+        <v>577587</v>
       </c>
       <c r="R22" t="n">
-        <v>6397197</v>
+        <v>6397168</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128587161</v>
+        <v>128588320</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577587</v>
+        <v>577330</v>
       </c>
       <c r="R23" t="n">
-        <v>6397168</v>
+        <v>6397251</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3135,7 +3135,7 @@
         <v>128589365</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>128589051</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3355,7 +3355,7 @@
         <v>128589413</v>
       </c>
       <c r="B26" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>128589098</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,17 +3565,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B28" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R28" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,10 +3682,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B29" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R29" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3795,7 +3795,7 @@
         <v>128589202</v>
       </c>
       <c r="B30" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
         <v>128589873</v>
       </c>
       <c r="B31" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>128588407</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>128588522</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>128589707</v>
       </c>
       <c r="B34" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>128587353</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>128589543</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128587466</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>128589077</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588564</v>
+        <v>128588456</v>
       </c>
       <c r="B39" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577316</v>
+        <v>577392</v>
       </c>
       <c r="R39" t="n">
-        <v>6397317</v>
+        <v>6397117</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,22 +4879,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128589031</v>
+        <v>128588564</v>
       </c>
       <c r="B40" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577525</v>
+        <v>577316</v>
       </c>
       <c r="R40" t="n">
-        <v>6397206</v>
+        <v>6397317</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,17 +4994,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128588456</v>
+        <v>128589031</v>
       </c>
       <c r="B41" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577392</v>
+        <v>577525</v>
       </c>
       <c r="R41" t="n">
-        <v>6397117</v>
+        <v>6397206</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,22 +5099,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128589604</v>
+        <v>128588364</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5154,14 +5154,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577299</v>
+        <v>577326</v>
       </c>
       <c r="R42" t="n">
-        <v>6397221</v>
+        <v>6397406</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5209,22 +5209,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128589315</v>
+        <v>128589604</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577563</v>
+        <v>577299</v>
       </c>
       <c r="R43" t="n">
-        <v>6397129</v>
+        <v>6397221</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128588364</v>
+        <v>128589315</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5374,14 +5374,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577326</v>
+        <v>577563</v>
       </c>
       <c r="R44" t="n">
-        <v>6397406</v>
+        <v>6397129</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,12 +5429,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5444,7 +5444,7 @@
         <v>128589521</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>128588509</v>
       </c>
       <c r="B46" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>128589006</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5770,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B48" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R48" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,10 +5880,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R49" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5983,17 +5983,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R50" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,22 +6088,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R51" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,69 +6198,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98651</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,19 +6301,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6323,7 +6322,7 @@
         <v>128588492</v>
       </c>
       <c r="B53" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6430,57 +6429,57 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128587548</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577533</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397187</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,18 +6520,19 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105719</v>
+        <v>105722</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand, Mats Oldenborg, Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6210,46 +6210,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R52" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,6 +6301,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6319,7 +6320,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128588492</v>
+        <v>128587548</v>
       </c>
       <c r="B53" t="n">
         <v>98659</v>
@@ -6349,12 +6350,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -6362,14 +6363,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>577314</v>
+        <v>577533</v>
       </c>
       <c r="R53" t="n">
-        <v>6397299</v>
+        <v>6397187</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6417,69 +6418,69 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587548</v>
+        <v>128587948</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577533</v>
+        <v>577405</v>
       </c>
       <c r="R54" t="n">
-        <v>6397187</v>
+        <v>6397127</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6520,19 +6521,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128587653</v>
+        <v>128588320</v>
       </c>
       <c r="B21" t="n">
         <v>98659</v>
@@ -2832,12 +2832,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2845,14 +2845,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577528</v>
+        <v>577330</v>
       </c>
       <c r="R21" t="n">
-        <v>6397197</v>
+        <v>6397251</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2900,19 +2900,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128587161</v>
+        <v>128587653</v>
       </c>
       <c r="B22" t="n">
         <v>98659</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577587</v>
+        <v>577528</v>
       </c>
       <c r="R22" t="n">
-        <v>6397168</v>
+        <v>6397197</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128588320</v>
+        <v>128587161</v>
       </c>
       <c r="B23" t="n">
         <v>98659</v>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3065,14 +3065,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577330</v>
+        <v>577587</v>
       </c>
       <c r="R23" t="n">
-        <v>6397251</v>
+        <v>6397168</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,12 +3120,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128589117</v>
+        <v>128588351</v>
       </c>
       <c r="B28" t="n">
         <v>98659</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577567</v>
+        <v>577334</v>
       </c>
       <c r="R28" t="n">
-        <v>6397167</v>
+        <v>6397251</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3682,7 +3682,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128588351</v>
+        <v>128589117</v>
       </c>
       <c r="B29" t="n">
         <v>98659</v>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577334</v>
+        <v>577567</v>
       </c>
       <c r="R29" t="n">
-        <v>6397251</v>
+        <v>6397167</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Eddy Kasselstrand, Magnus Kasselstrand, Gunilla Nilsson, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128588456</v>
+        <v>128588564</v>
       </c>
       <c r="B39" t="n">
         <v>98659</v>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -4824,14 +4824,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>577392</v>
+        <v>577316</v>
       </c>
       <c r="R39" t="n">
-        <v>6397117</v>
+        <v>6397317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4879,19 +4879,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128588564</v>
+        <v>128589031</v>
       </c>
       <c r="B40" t="n">
         <v>98659</v>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4938,10 +4938,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>577316</v>
+        <v>577525</v>
       </c>
       <c r="R40" t="n">
-        <v>6397317</v>
+        <v>6397206</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5001,7 +5001,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128589031</v>
+        <v>128588456</v>
       </c>
       <c r="B41" t="n">
         <v>98659</v>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -5044,14 +5044,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>577525</v>
+        <v>577392</v>
       </c>
       <c r="R41" t="n">
-        <v>6397206</v>
+        <v>6397117</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5099,19 +5099,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128588364</v>
+        <v>128589604</v>
       </c>
       <c r="B42" t="n">
         <v>98659</v>
@@ -5141,12 +5141,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -5154,14 +5154,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>577326</v>
+        <v>577299</v>
       </c>
       <c r="R42" t="n">
-        <v>6397406</v>
+        <v>6397221</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5209,19 +5209,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128589604</v>
+        <v>128589315</v>
       </c>
       <c r="B43" t="n">
         <v>98659</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>577299</v>
+        <v>577563</v>
       </c>
       <c r="R43" t="n">
-        <v>6397221</v>
+        <v>6397129</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128589315</v>
+        <v>128588364</v>
       </c>
       <c r="B44" t="n">
         <v>98659</v>
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -5374,14 +5374,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>577563</v>
+        <v>577326</v>
       </c>
       <c r="R44" t="n">
-        <v>6397129</v>
+        <v>6397406</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5429,12 +5429,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5770,7 +5770,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128588696</v>
+        <v>128588384</v>
       </c>
       <c r="B48" t="n">
         <v>98659</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R48" t="n">
-        <v>6397374</v>
+        <v>6397265</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128588384</v>
+        <v>128588696</v>
       </c>
       <c r="B49" t="n">
         <v>98659</v>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>577333</v>
+        <v>577297</v>
       </c>
       <c r="R49" t="n">
-        <v>6397265</v>
+        <v>6397374</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5990,7 +5990,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128589459</v>
+        <v>128588387</v>
       </c>
       <c r="B50" t="n">
         <v>98659</v>
@@ -6020,12 +6020,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -6033,14 +6033,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storö-Ankarsrum, Sm</t>
+          <t>Storö, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577497</v>
+        <v>577332</v>
       </c>
       <c r="R50" t="n">
-        <v>6397021</v>
+        <v>6397322</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6088,19 +6088,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128588387</v>
+        <v>128589459</v>
       </c>
       <c r="B51" t="n">
         <v>98659</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -6143,14 +6143,14 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Storö, Ankarsrum, Sm</t>
+          <t>Storö-Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577332</v>
+        <v>577497</v>
       </c>
       <c r="R51" t="n">
-        <v>6397322</v>
+        <v>6397021</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6198,58 +6198,58 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Magnus Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128588492</v>
+        <v>128587948</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577314</v>
+        <v>577405</v>
       </c>
       <c r="R52" t="n">
-        <v>6397299</v>
+        <v>6397127</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,7 +6301,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6430,46 +6429,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128587948</v>
+        <v>128588492</v>
       </c>
       <c r="B54" t="n">
-        <v>57720</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6477,10 +6476,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>577405</v>
+        <v>577314</v>
       </c>
       <c r="R54" t="n">
-        <v>6397127</v>
+        <v>6397299</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,6 +6520,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Gunilla Nilsson, Larsgunnar Nilsson, Eddy Kasselstrand, Magnus Kasselstrand, Mats Oldenborg, Stefan Kasselstrand</t>
+          <t>Stefan Kasselstrand, Mats Oldenborg, Magnus Kasselstrand, Eddy Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Mats Oldenborg, Stefan Kasselstrand, Eddy Kasselstrand, Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand , Eddy Kasselstrand, Stefan Kasselstrand, Mats Oldenborg, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96111</v>
+        <v>96118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -6542,7 +6542,7 @@
         <v>128746398</v>
       </c>
       <c r="B55" t="n">
-        <v>105732</v>
+        <v>105741</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>128745964</v>
       </c>
       <c r="B56" t="n">
-        <v>92233</v>
+        <v>92242</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>128747154</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>128746440</v>
       </c>
       <c r="B58" t="n">
-        <v>92165</v>
+        <v>92174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>128745659</v>
       </c>
       <c r="B59" t="n">
-        <v>92233</v>
+        <v>92242</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96118</v>
+        <v>96120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11247,6 +11247,1158 @@
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129357463</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91501</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Långsjön, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>577594</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6396610</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129359409</v>
+      </c>
+      <c r="B99" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>577504</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6396930</v>
+      </c>
+      <c r="S99" t="n">
+        <v>20</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jonas Hedin, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129360878</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91562</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>577504</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6396930</v>
+      </c>
+      <c r="S100" t="n">
+        <v>20</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jonas Hedin, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129368962</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91502</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Mellanängen, Mellanängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>577263</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6397764</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129357841</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92174</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Bockberget, Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>577502</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6396857</v>
+      </c>
+      <c r="S102" t="n">
+        <v>25</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129369965</v>
+      </c>
+      <c r="B103" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>577397</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6396969</v>
+      </c>
+      <c r="S103" t="n">
+        <v>20</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>i granlåga</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Jonas Hedin, Jesper Hansson, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129369996</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91543</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Storö, Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>577387</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6397249</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129357184</v>
+      </c>
+      <c r="B105" t="n">
+        <v>85214</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>241</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Gransotdyna</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Camarops tubulina</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Långsjön, Långsjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>577594</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6396610</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129357012</v>
+      </c>
+      <c r="B106" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>577537</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6396561</v>
+      </c>
+      <c r="S106" t="n">
+        <v>20</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129367994</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91502</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>577307</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6397639</v>
+      </c>
+      <c r="S107" t="n">
+        <v>20</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>på grov ek med bhd 60 cm</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129357641</v>
+      </c>
+      <c r="B108" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Bockberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>577453</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6396762</v>
+      </c>
+      <c r="S108" t="n">
+        <v>20</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jonas Hedin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96120</v>
+        <v>96146</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,48 +11249,53 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B98" t="n">
-        <v>91501</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R98" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11317,19 +11322,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11344,52 +11339,47 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>4779</v>
+        <v>91560</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11432,6 +11422,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11458,10 +11453,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B100" t="n">
-        <v>91562</v>
+        <v>91499</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11469,37 +11464,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R100" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11526,14 +11521,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91502</v>
+        <v>91499</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92174</v>
+        <v>92189</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91543</v>
+        <v>91540</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>129357184</v>
       </c>
       <c r="B105" t="n">
-        <v>85214</v>
+        <v>85215</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>129367994</v>
       </c>
       <c r="B107" t="n">
-        <v>91502</v>
+        <v>91499</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91561</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11327,6 +11322,11 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11344,42 +11344,47 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Pontus Axén, Jonas Hedin</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129359409</v>
       </c>
       <c r="B99" t="n">
-        <v>91560</v>
+        <v>4779</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11422,11 +11427,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92189</v>
+        <v>92190</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11988,48 +11988,53 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129357184</v>
+        <v>129357012</v>
       </c>
       <c r="B105" t="n">
-        <v>85215</v>
+        <v>5177</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>241</v>
+        <v>100526</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>577594</v>
+        <v>577537</v>
       </c>
       <c r="R105" t="n">
-        <v>6396610</v>
+        <v>6396561</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12056,19 +12061,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12083,65 +12078,60 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357012</v>
+        <v>129357184</v>
       </c>
       <c r="B106" t="n">
-        <v>5177</v>
+        <v>85215</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100526</v>
+        <v>241</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>577537</v>
+        <v>577594</v>
       </c>
       <c r="R106" t="n">
-        <v>6396561</v>
+        <v>6396610</v>
       </c>
       <c r="S106" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12168,9 +12158,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12185,12 +12185,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12399,6 +12399,107 @@
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129410178</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Storö, Sm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>577584</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6396611</v>
+      </c>
+      <c r="S109" t="n">
+        <v>20</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11344,60 +11344,55 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jonas Hedin</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129359409</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>4779</v>
+        <v>91499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102306</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11424,9 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91499</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12090,10 +12090,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129357184</v>
+        <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>85215</v>
+        <v>91499</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12101,37 +12101,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>241</v>
+        <v>5445</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Shear</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Storö, Sm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>577594</v>
+        <v>577307</v>
       </c>
       <c r="R106" t="n">
-        <v>6396610</v>
+        <v>6397639</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12158,19 +12158,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:11</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>på grov ek med bhd 60 cm</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12185,57 +12180,62 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129367994</v>
+        <v>129357641</v>
       </c>
       <c r="B107" t="n">
-        <v>91499</v>
+        <v>5177</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5445</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Storö, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>577307</v>
+        <v>577453</v>
       </c>
       <c r="R107" t="n">
-        <v>6397639</v>
+        <v>6396762</v>
       </c>
       <c r="S107" t="n">
         <v>20</v>
@@ -12268,11 +12268,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>på grov ek med bhd 60 cm</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12299,10 +12294,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129357641</v>
+        <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>5177</v>
+        <v>91504</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12310,39 +12305,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Storö, Sm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>577453</v>
+        <v>577584</v>
       </c>
       <c r="R108" t="n">
-        <v>6396762</v>
+        <v>6396611</v>
       </c>
       <c r="S108" t="n">
         <v>20</v>
@@ -12383,122 +12376,22 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>129410178</v>
-      </c>
-      <c r="B109" t="n">
-        <v>91504</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Fuscoporia viticola</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Storö, Sm</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>577584</v>
-      </c>
-      <c r="R109" t="n">
-        <v>6396611</v>
-      </c>
-      <c r="S109" t="n">
-        <v>20</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AD109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF109" t="inlineStr"/>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT109" t="inlineStr"/>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92190</v>
+        <v>92193</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11142,7 +11142,7 @@
         <v>128895504</v>
       </c>
       <c r="B97" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91502</v>
+        <v>91504</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91502</v>
+        <v>91504</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92193</v>
+        <v>92195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91502</v>
+        <v>91504</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11252,7 +11252,7 @@
         <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92195</v>
+        <v>92199</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11252,7 +11252,7 @@
         <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91508</v>
+        <v>91509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91508</v>
+        <v>91509</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92199</v>
+        <v>92200</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91508</v>
+        <v>91509</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
+          <t>Jonas Hedin, Magnus Danbolt, Pontus Axén, Jesper Hansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Magnus Danbolt, Pontus Axén, Jesper Hansson</t>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11252,7 +11252,7 @@
         <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91509</v>
+        <v>91512</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91509</v>
+        <v>91512</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92200</v>
+        <v>92203</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91509</v>
+        <v>91512</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,35 +11249,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129360878</v>
+        <v>129359409</v>
       </c>
       <c r="B98" t="n">
-        <v>91574</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11320,11 +11325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>91512</v>
+        <v>91574</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R99" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,19 +11419,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,65 +11441,60 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129359409</v>
+        <v>129357463</v>
       </c>
       <c r="B100" t="n">
-        <v>4779</v>
+        <v>91512</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102306</v>
+        <v>5445</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R100" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11531,9 +11521,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91574</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11325,6 +11320,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91574</v>
+        <v>91512</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91512</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91574</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11325,6 +11320,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91574</v>
+        <v>91512</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91512</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
+          <t>Jesper Hansson, Pontus Axén, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,35 +11249,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129360878</v>
+        <v>129359409</v>
       </c>
       <c r="B98" t="n">
-        <v>91574</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11320,11 +11325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>91512</v>
+        <v>91574</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R99" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,19 +11419,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,65 +11441,60 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129359409</v>
+        <v>129357463</v>
       </c>
       <c r="B100" t="n">
-        <v>4779</v>
+        <v>91512</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102306</v>
+        <v>5445</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R100" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11531,9 +11521,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Pontus Axén, Jonas Hedin, Magnus Danbolt</t>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91602</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11325,6 +11320,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91574</v>
+        <v>91540</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91512</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91512</v>
+        <v>91540</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91512</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,35 +11249,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129360878</v>
+        <v>129359409</v>
       </c>
       <c r="B98" t="n">
-        <v>91602</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11320,11 +11325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>91540</v>
+        <v>91602</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R99" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,19 +11419,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,65 +11441,60 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129359409</v>
+        <v>129357463</v>
       </c>
       <c r="B100" t="n">
-        <v>4779</v>
+        <v>91540</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102306</v>
+        <v>5445</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R100" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11531,9 +11521,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91608</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11325,6 +11320,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91602</v>
+        <v>91546</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91540</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92231</v>
+        <v>92237</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>91546</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,35 +11249,40 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129360878</v>
+        <v>129359409</v>
       </c>
       <c r="B98" t="n">
-        <v>91608</v>
+        <v>4779</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11320,11 +11325,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>91546</v>
+        <v>91609</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R99" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,19 +11419,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,65 +11441,60 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129359409</v>
+        <v>129357463</v>
       </c>
       <c r="B100" t="n">
-        <v>4779</v>
+        <v>91547</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>102306</v>
+        <v>5445</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R100" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11531,9 +11521,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91546</v>
+        <v>91547</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Jesper Hansson, Pontus Axén</t>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91546</v>
+        <v>91547</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,40 +11249,35 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129359409</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>4779</v>
+        <v>91614</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Bockberget, Sm</t>
@@ -11325,6 +11320,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,10 +11351,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91609</v>
+        <v>91552</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11441,60 +11446,65 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129357463</v>
+        <v>129359409</v>
       </c>
       <c r="B100" t="n">
-        <v>91547</v>
+        <v>4779</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5445</v>
+        <v>102306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R100" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11521,19 +11531,9 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11548,12 +11548,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11563,7 +11563,7 @@
         <v>129368962</v>
       </c>
       <c r="B101" t="n">
-        <v>91547</v>
+        <v>91552</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>129357841</v>
       </c>
       <c r="B102" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jesper Hansson, Jonas Hedin</t>
+          <t>Jonas Hedin, Jesper Hansson, Pontus Axén</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11884,7 +11884,7 @@
         <v>129369996</v>
       </c>
       <c r="B104" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>129367994</v>
       </c>
       <c r="B106" t="n">
-        <v>91547</v>
+        <v>91552</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,10 +11249,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B98" t="n">
-        <v>91614</v>
+        <v>91552</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11260,37 +11260,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R98" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11317,14 +11317,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11339,22 +11344,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B99" t="n">
-        <v>91552</v>
+        <v>91614</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,37 +11367,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R99" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11419,19 +11424,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,12 +11446,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -11249,10 +11249,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129357463</v>
+        <v>129360878</v>
       </c>
       <c r="B98" t="n">
-        <v>91552</v>
+        <v>91614</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11260,37 +11260,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5445</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långsjön, Långsjön, Sm</t>
+          <t>Bockberget, Sm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>577594</v>
+        <v>577504</v>
       </c>
       <c r="R98" t="n">
-        <v>6396610</v>
+        <v>6396930</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11317,19 +11317,14 @@
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:29</t>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>på gammal slätbarkig tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11344,22 +11339,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jonas Hedin, Pontus Axén</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129360878</v>
+        <v>129357463</v>
       </c>
       <c r="B99" t="n">
-        <v>91614</v>
+        <v>91552</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11367,37 +11362,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5442</v>
+        <v>5445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Bockberget, Sm</t>
+          <t>Långsjön, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577504</v>
+        <v>577594</v>
       </c>
       <c r="R99" t="n">
-        <v>6396930</v>
+        <v>6396610</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11424,14 +11419,19 @@
           <t>2025-10-27</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på gammal slätbarkig tall</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,12 +11446,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Hedin</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Hedin, Pontus Axén</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
+          <t>Jesper Hansson, Pontus Axén, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -12297,7 +12297,7 @@
         <v>129410178</v>
       </c>
       <c r="B108" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Pontus Axén, Jonas Hedin, Magnus Danbolt</t>
+          <t>Pontus Axén, Jesper Hansson, Jonas Hedin, Magnus Danbolt</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -10577,7 +10577,7 @@
         <v>0</v>
       </c>
       <c r="AE91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101301</v>
+        <v>101304</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91265</v>
+        <v>91271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91271</v>
+        <v>91281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91281</v>
+        <v>91282</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91282</v>
+        <v>91283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91283</v>
+        <v>91285</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 42892-2025 artfynd.xlsx
+++ b/artfynd/A 42892-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>122744580</v>
       </c>
       <c r="B3" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>122744612</v>
       </c>
       <c r="B4" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122744600</v>
       </c>
       <c r="B5" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>122744623</v>
       </c>
       <c r="B6" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>122744601</v>
       </c>
       <c r="B7" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>122744603</v>
       </c>
       <c r="B8" t="n">
-        <v>91285</v>
+        <v>91286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>122744607</v>
       </c>
       <c r="B9" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>122744598</v>
       </c>
       <c r="B10" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>122744615</v>
       </c>
       <c r="B11" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>122744602</v>
       </c>
       <c r="B12" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>122744599</v>
       </c>
       <c r="B13" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
